--- a/England 2026/incd_tbl.xlsx
+++ b/England 2026/incd_tbl.xlsx
@@ -62,7 +62,7 @@
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.7109375" customWidth="true"/>
     <col min="6" max="6" width="11.7109375" customWidth="true"/>
-    <col min="7" max="7" width="10.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
     <col min="8" max="8" width="11.7109375" customWidth="true"/>
     <col min="9" max="9" width="11.7109375" customWidth="true"/>
     <col min="10" max="10" width="11.7109375" customWidth="true"/>
@@ -111,61 +111,61 @@
         <v>8.4280112485773184</v>
       </c>
       <c r="I1" s="0">
-        <v>9.4512769942782082</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J1" s="0">
-        <v>10.059944639406408</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K1" s="0">
-        <v>9.7456940185883916</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L1" s="0">
-        <v>9.7071557732318237</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M1" s="0">
-        <v>9.6857483781767169</v>
+        <v>9.6857500401426773</v>
       </c>
       <c r="N1" s="0">
-        <v>9.6583362039038132</v>
+        <v>9.658336575305162</v>
       </c>
       <c r="O1" s="0">
-        <v>9.6298166987383276</v>
+        <v>9.6298121957845932</v>
       </c>
       <c r="P1" s="0">
-        <v>9.6020560023134163</v>
+        <v>9.6020527832841118</v>
       </c>
       <c r="Q1" s="0">
-        <v>9.575784158924499</v>
+        <v>9.5757822343298127</v>
       </c>
       <c r="R1" s="0">
-        <v>9.5512600637132277</v>
+        <v>9.5512601135718907</v>
       </c>
       <c r="S1" s="0">
-        <v>9.5285365197909293</v>
+        <v>9.5285359482134275</v>
       </c>
       <c r="T1" s="0">
-        <v>9.5075547060756023</v>
+        <v>9.5075540836168191</v>
       </c>
       <c r="U1" s="0">
-        <v>9.4882049457057214</v>
+        <v>9.4882051115490693</v>
       </c>
       <c r="V1" s="0">
-        <v>9.4703535397322209</v>
+        <v>9.4703535498780713</v>
       </c>
       <c r="W1" s="0">
-        <v>9.4538567182265663</v>
+        <v>9.4538567080797336</v>
       </c>
       <c r="X1" s="0">
-        <v>9.4385738522340308</v>
+        <v>9.4385738271529078</v>
       </c>
       <c r="Y1" s="0">
-        <v>9.424371546664414</v>
+        <v>9.4243715009645825</v>
       </c>
       <c r="Z1" s="0">
-        <v>9.4111268624387172</v>
+        <v>9.4111268785990667</v>
       </c>
       <c r="AA1" s="0">
-        <v>9.398729080461548</v>
+        <v>9.3987291342051016</v>
       </c>
     </row>
     <row r="2">
@@ -194,61 +194,61 @@
         <v>9.2460677010700643</v>
       </c>
       <c r="I2" s="0">
-        <v>10.319411064577873</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J2" s="0">
-        <v>10.963531913970748</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K2" s="0">
-        <v>10.631212235509658</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L2" s="0">
-        <v>10.582918320691901</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M2" s="0">
-        <v>10.556063360892237</v>
+        <v>10.556061874038596</v>
       </c>
       <c r="N2" s="0">
-        <v>10.529487206280939</v>
+        <v>10.529484859871472</v>
       </c>
       <c r="O2" s="0">
-        <v>10.5020603661845</v>
+        <v>10.50206294203244</v>
       </c>
       <c r="P2" s="0">
-        <v>10.475413536026878</v>
+        <v>10.475414523021961</v>
       </c>
       <c r="Q2" s="0">
-        <v>10.45022896630317</v>
+        <v>10.450229567772194</v>
       </c>
       <c r="R2" s="0">
-        <v>10.426785727520697</v>
+        <v>10.426785054414284</v>
       </c>
       <c r="S2" s="0">
-        <v>10.405156935158733</v>
+        <v>10.405157331800316</v>
       </c>
       <c r="T2" s="0">
-        <v>10.385307905483197</v>
+        <v>10.385307973584723</v>
       </c>
       <c r="U2" s="0">
-        <v>10.367141466266563</v>
+        <v>10.36714130870234</v>
       </c>
       <c r="V2" s="0">
-        <v>10.350530221264849</v>
+        <v>10.350530265165538</v>
       </c>
       <c r="W2" s="0">
-        <v>10.335334655985106</v>
+        <v>10.335334688787993</v>
       </c>
       <c r="X2" s="0">
-        <v>10.321413151436218</v>
+        <v>10.321413273716313</v>
       </c>
       <c r="Y2" s="0">
-        <v>10.308629174821247</v>
+        <v>10.308629287305552</v>
       </c>
       <c r="Z2" s="0">
-        <v>10.296855094438181</v>
+        <v>10.296855163938661</v>
       </c>
       <c r="AA2" s="0">
-        <v>10.285974193557053</v>
+        <v>10.285974287558572</v>
       </c>
     </row>
     <row r="3">
@@ -277,1306 +277,1306 @@
         <v>9.6501119343113828</v>
       </c>
       <c r="I3" s="0">
-        <v>10.752675680898596</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J3" s="0">
-        <v>11.440108190522142</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K3" s="0">
-        <v>11.082722783634297</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L3" s="0">
-        <v>11.022275573951291</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M3" s="0">
-        <v>10.989360441527115</v>
+        <v>10.989360058749195</v>
       </c>
       <c r="N3" s="0">
-        <v>10.954520242439008</v>
+        <v>10.954519152270072</v>
       </c>
       <c r="O3" s="0">
-        <v>10.920293465913593</v>
+        <v>10.920294928454025</v>
       </c>
       <c r="P3" s="0">
-        <v>10.887684211239712</v>
+        <v>10.8876849852766</v>
       </c>
       <c r="Q3" s="0">
-        <v>10.857053285032283</v>
+        <v>10.857053622780782</v>
       </c>
       <c r="R3" s="0">
-        <v>10.828493130503167</v>
+        <v>10.828492841654992</v>
       </c>
       <c r="S3" s="0">
-        <v>10.801965484126406</v>
+        <v>10.801965919078212</v>
       </c>
       <c r="T3" s="0">
-        <v>10.777369511853735</v>
+        <v>10.777369599891248</v>
       </c>
       <c r="U3" s="0">
-        <v>10.754572095865433</v>
+        <v>10.754572137535813</v>
       </c>
       <c r="V3" s="0">
-        <v>10.733428522932163</v>
+        <v>10.73342867399837</v>
       </c>
       <c r="W3" s="0">
-        <v>10.713792850698242</v>
+        <v>10.713792948289008</v>
       </c>
       <c r="X3" s="0">
-        <v>10.695523429436589</v>
+        <v>10.695523610769866</v>
       </c>
       <c r="Y3" s="0">
-        <v>10.680867547098739</v>
+        <v>10.680867727816491</v>
       </c>
       <c r="Z3" s="0">
-        <v>10.667342379531252</v>
+        <v>10.66734259717995</v>
       </c>
       <c r="AA3" s="0">
-        <v>10.654771538173289</v>
+        <v>10.654771696612539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>8.5954438039823398</v>
+        <v>10.844516223301909</v>
       </c>
       <c r="B4" s="0">
-        <v>9.4662077193616909</v>
+        <v>9.9379482936889438</v>
       </c>
       <c r="C4" s="0">
-        <v>9.9468318711430612</v>
+        <v>9.1112377092064634</v>
       </c>
       <c r="D4" s="0">
-        <v>9.1163278522964397</v>
+        <v>8.5954438328424629</v>
       </c>
       <c r="E4" s="0">
-        <v>8.8826739706186579</v>
+        <v>8.359478635847557</v>
       </c>
       <c r="F4" s="0">
-        <v>8.6198166718301348</v>
+        <v>8.0975678771514836</v>
       </c>
       <c r="G4" s="0">
-        <v>8.4205221338624021</v>
+        <v>7.9067622702830578</v>
       </c>
       <c r="H4" s="0">
-        <v>8.8709273527150625</v>
+        <v>8.4280112485773184</v>
       </c>
       <c r="I4" s="0">
-        <v>9.8068576809349732</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J4" s="0">
-        <v>10.45244529472383</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K4" s="0">
-        <v>10.297435374431931</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L4" s="0">
-        <v>10.275968773389657</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M4" s="0">
-        <v>10.259914782589165</v>
+        <v>9.6857505170618836</v>
       </c>
       <c r="N4" s="0">
-        <v>10.225305450222677</v>
+        <v>9.6441394566153154</v>
       </c>
       <c r="O4" s="0">
-        <v>10.126385611199936</v>
+        <v>9.5418015830210994</v>
       </c>
       <c r="P4" s="0">
-        <v>9.9686371865353909</v>
+        <v>9.3856059250938078</v>
       </c>
       <c r="Q4" s="0">
-        <v>9.770990538192958</v>
+        <v>9.1929939008524961</v>
       </c>
       <c r="R4" s="0">
-        <v>9.548694763968161</v>
+        <v>8.9798790808043218</v>
       </c>
       <c r="S4" s="0">
-        <v>9.3154551226127342</v>
+        <v>8.7594836540817234</v>
       </c>
       <c r="T4" s="0">
-        <v>9.0849350126027435</v>
+        <v>8.5417432871447385</v>
       </c>
       <c r="U4" s="0">
-        <v>8.8638807232454582</v>
+        <v>8.3333043347006583</v>
       </c>
       <c r="V4" s="0">
-        <v>8.656098372107861</v>
+        <v>8.1452874580427981</v>
       </c>
       <c r="W4" s="0">
-        <v>8.4836994804103512</v>
+        <v>7.9970906491825975</v>
       </c>
       <c r="X4" s="0">
-        <v>8.3482933361700216</v>
+        <v>7.8796822949429259</v>
       </c>
       <c r="Y4" s="0">
-        <v>8.2384052194585067</v>
+        <v>7.7840243292286973</v>
       </c>
       <c r="Z4" s="0">
-        <v>8.1468996254467783</v>
+        <v>7.704243736958051</v>
       </c>
       <c r="AA4" s="0">
-        <v>8.0691109436100099</v>
+        <v>7.6363459237116755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>8.3594786076326031</v>
+        <v>11.877427748784047</v>
       </c>
       <c r="B5" s="0">
-        <v>9.2130073636349632</v>
+        <v>10.908563108108515</v>
       </c>
       <c r="C5" s="0">
-        <v>9.6612285104853086</v>
+        <v>10.020654879047406</v>
       </c>
       <c r="D5" s="0">
-        <v>9.5324155660250352</v>
+        <v>9.4662077295226954</v>
       </c>
       <c r="E5" s="0">
-        <v>9.2675269815294428</v>
+        <v>9.2130073737036753</v>
       </c>
       <c r="F5" s="0">
-        <v>8.9922326865357594</v>
+        <v>8.9244193911582883</v>
       </c>
       <c r="G5" s="0">
-        <v>8.7732251075719177</v>
+        <v>8.7026070100774877</v>
       </c>
       <c r="H5" s="0">
-        <v>9.1850570691558637</v>
+        <v>9.2460677010700643</v>
       </c>
       <c r="I5" s="0">
-        <v>10.107495915644407</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J5" s="0">
-        <v>10.759004813883564</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K5" s="0">
-        <v>10.554294693454978</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L5" s="0">
-        <v>10.49182737581431</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M5" s="0">
-        <v>10.450000687892132</v>
+        <v>10.556062128219022</v>
       </c>
       <c r="N5" s="0">
-        <v>10.400783607879402</v>
+        <v>10.513278736808372</v>
       </c>
       <c r="O5" s="0">
-        <v>10.286222813953042</v>
+        <v>10.401193269857719</v>
       </c>
       <c r="P5" s="0">
-        <v>10.123532578955389</v>
+        <v>10.22711613395089</v>
       </c>
       <c r="Q5" s="0">
-        <v>9.930441521067646</v>
+        <v>10.011175416403203</v>
       </c>
       <c r="R5" s="0">
-        <v>9.7279475595445639</v>
+        <v>9.7716298265678798</v>
       </c>
       <c r="S5" s="0">
-        <v>9.5167656807205958</v>
+        <v>9.525292329797896</v>
       </c>
       <c r="T5" s="0">
-        <v>9.2778842133865229</v>
+        <v>9.2832011940109354</v>
       </c>
       <c r="U5" s="0">
-        <v>9.0619138097689298</v>
+        <v>9.0507521255164232</v>
       </c>
       <c r="V5" s="0">
-        <v>8.8718893636373899</v>
+        <v>8.8401039228370717</v>
       </c>
       <c r="W5" s="0">
-        <v>8.7205961259609293</v>
+        <v>8.6726493263471145</v>
       </c>
       <c r="X5" s="0">
-        <v>8.5864951113859949</v>
+        <v>8.5386084676251368</v>
       </c>
       <c r="Y5" s="0">
-        <v>8.4753162666377584</v>
+        <v>8.4281001784212162</v>
       </c>
       <c r="Z5" s="0">
-        <v>8.3813098855252619</v>
+        <v>8.334834305711393</v>
       </c>
       <c r="AA5" s="0">
-        <v>8.3003762655894562</v>
+        <v>8.2549521744033143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>8.097571246065792</v>
+        <v>12.509011056149573</v>
       </c>
       <c r="B6" s="0">
-        <v>8.9244194382927553</v>
+        <v>11.482052228974633</v>
       </c>
       <c r="C6" s="0">
-        <v>9.3433358579822734</v>
+        <v>10.542165939779661</v>
       </c>
       <c r="D6" s="0">
-        <v>9.7802141663484825</v>
+        <v>9.9468320606150264</v>
       </c>
       <c r="E6" s="0">
-        <v>9.540502667192488</v>
+        <v>9.6612286475170031</v>
       </c>
       <c r="F6" s="0">
-        <v>9.2669915682210515</v>
+        <v>9.3433398302568396</v>
       </c>
       <c r="G6" s="0">
-        <v>9.0527962652444494</v>
+        <v>9.1084722446249629</v>
       </c>
       <c r="H6" s="0">
-        <v>9.4372404495201589</v>
+        <v>9.6501119343113828</v>
       </c>
       <c r="I6" s="0">
-        <v>10.494338689836615</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J6" s="0">
-        <v>11.251091074130811</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K6" s="0">
-        <v>11.102139979890151</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L6" s="0">
-        <v>11.078342038253641</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M6" s="0">
-        <v>11.06187021753113</v>
+        <v>10.989360509383236</v>
       </c>
       <c r="N6" s="0">
-        <v>11.024644458396443</v>
+        <v>10.937092993241329</v>
       </c>
       <c r="O6" s="0">
-        <v>10.912620725367544</v>
+        <v>10.811776671280109</v>
       </c>
       <c r="P6" s="0">
-        <v>10.73225164200872</v>
+        <v>10.621206349412258</v>
       </c>
       <c r="Q6" s="0">
-        <v>10.505859511773862</v>
+        <v>10.387395891121987</v>
       </c>
       <c r="R6" s="0">
-        <v>10.253469548276477</v>
+        <v>10.140634603481047</v>
       </c>
       <c r="S6" s="0">
-        <v>9.9914408549844218</v>
+        <v>9.8928499628697484</v>
       </c>
       <c r="T6" s="0">
-        <v>9.7318705279032116</v>
+        <v>9.6475770872574422</v>
       </c>
       <c r="U6" s="0">
-        <v>9.4828413059563577</v>
+        <v>9.4119400123417041</v>
       </c>
       <c r="V6" s="0">
-        <v>9.2573774377598657</v>
+        <v>9.1981958357982432</v>
       </c>
       <c r="W6" s="0">
-        <v>9.0798452454098229</v>
+        <v>9.0282547638252488</v>
       </c>
       <c r="X6" s="0">
-        <v>8.9405406080653691</v>
+        <v>8.8922517959715854</v>
       </c>
       <c r="Y6" s="0">
-        <v>8.8275921961027706</v>
+        <v>8.7800439175468181</v>
       </c>
       <c r="Z6" s="0">
-        <v>8.733711381911208</v>
+        <v>8.6851924480019207</v>
       </c>
       <c r="AA6" s="0">
-        <v>8.6540784168641487</v>
+        <v>8.6034317166027368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>7.9067622134855844</v>
+        <v>10.844516223301909</v>
       </c>
       <c r="B7" s="0">
-        <v>8.7026071277739785</v>
+        <v>9.9379482936889438</v>
       </c>
       <c r="C7" s="0">
-        <v>9.10847506922957</v>
+        <v>9.1112377092064634</v>
       </c>
       <c r="D7" s="0">
-        <v>9.1163278522964397</v>
+        <v>8.5954438328424629</v>
       </c>
       <c r="E7" s="0">
-        <v>8.8826739706186579</v>
+        <v>8.359478635847557</v>
       </c>
       <c r="F7" s="0">
-        <v>8.6198166718301348</v>
+        <v>8.0975678771514836</v>
       </c>
       <c r="G7" s="0">
-        <v>8.4205221338624021</v>
+        <v>7.9067622702830578</v>
       </c>
       <c r="H7" s="0">
-        <v>8.8709273527150625</v>
+        <v>8.4280112485773184</v>
       </c>
       <c r="I7" s="0">
-        <v>9.8068576809349732</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J7" s="0">
-        <v>10.45244529472383</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K7" s="0">
-        <v>10.297435374431931</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L7" s="0">
-        <v>10.275968773389657</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M7" s="0">
-        <v>10.259914782552505</v>
+        <v>9.6857505169456886</v>
       </c>
       <c r="N7" s="0">
-        <v>10.225117872871634</v>
+        <v>9.6439573518454989</v>
       </c>
       <c r="O7" s="0">
-        <v>10.125603151592058</v>
+        <v>9.541037434566185</v>
       </c>
       <c r="P7" s="0">
-        <v>9.9673033507781757</v>
+        <v>9.3843092681960325</v>
       </c>
       <c r="Q7" s="0">
-        <v>9.7692353623139976</v>
+        <v>9.191307277792756</v>
       </c>
       <c r="R7" s="0">
-        <v>9.547214199214249</v>
+        <v>8.9779382024705523</v>
       </c>
       <c r="S7" s="0">
-        <v>9.3138647230904326</v>
+        <v>8.7574098198385109</v>
       </c>
       <c r="T7" s="0">
-        <v>9.0833133521313325</v>
+        <v>8.5396440526697113</v>
       </c>
       <c r="U7" s="0">
-        <v>8.862306317178442</v>
+        <v>8.331274504805009</v>
       </c>
       <c r="V7" s="0">
-        <v>8.6545663156388759</v>
+        <v>8.1435921568140923</v>
       </c>
       <c r="W7" s="0">
-        <v>8.482852967647144</v>
+        <v>7.9962046146334283</v>
       </c>
       <c r="X7" s="0">
-        <v>8.3481337273252869</v>
+        <v>7.8796056185044288</v>
       </c>
       <c r="Y7" s="0">
-        <v>8.2388430597366007</v>
+        <v>7.7846520391315011</v>
       </c>
       <c r="Z7" s="0">
-        <v>8.1478552788120666</v>
+        <v>7.7054819410712163</v>
       </c>
       <c r="AA7" s="0">
-        <v>8.0705228756936212</v>
+        <v>7.6381214386418224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>8.4280102484644583</v>
+        <v>11.877427748784047</v>
       </c>
       <c r="B8" s="0">
-        <v>9.2460707886965547</v>
+        <v>10.908563108108515</v>
       </c>
       <c r="C8" s="0">
-        <v>9.6501143813637587</v>
+        <v>10.020654879047406</v>
       </c>
       <c r="D8" s="0">
-        <v>9.5324155660250352</v>
+        <v>9.4662077295226954</v>
       </c>
       <c r="E8" s="0">
-        <v>9.2675269815294428</v>
+        <v>9.2130073737036753</v>
       </c>
       <c r="F8" s="0">
-        <v>8.9922326865357594</v>
+        <v>8.9244193911582883</v>
       </c>
       <c r="G8" s="0">
-        <v>8.7732251075719177</v>
+        <v>8.7026070100774877</v>
       </c>
       <c r="H8" s="0">
-        <v>9.1850570691558637</v>
+        <v>9.2460677010700643</v>
       </c>
       <c r="I8" s="0">
-        <v>10.107495915644407</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J8" s="0">
-        <v>10.759004813883564</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K8" s="0">
-        <v>10.554294693454978</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L8" s="0">
-        <v>10.49182737581431</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M8" s="0">
-        <v>10.450000687856178</v>
+        <v>10.556062128182061</v>
       </c>
       <c r="N8" s="0">
-        <v>10.400627061728004</v>
+        <v>10.513101383994584</v>
       </c>
       <c r="O8" s="0">
-        <v>10.28588233341662</v>
+        <v>10.400447265232648</v>
       </c>
       <c r="P8" s="0">
-        <v>10.122957518620241</v>
+        <v>10.225847584326225</v>
       </c>
       <c r="Q8" s="0">
-        <v>9.9288640809992863</v>
+        <v>10.00952050506582</v>
       </c>
       <c r="R8" s="0">
-        <v>9.726118528151158</v>
+        <v>9.7697183005373471</v>
       </c>
       <c r="S8" s="0">
-        <v>9.5147935585976473</v>
+        <v>9.5234020755088356</v>
       </c>
       <c r="T8" s="0">
-        <v>9.2761965515536264</v>
+        <v>9.2812738798992971</v>
       </c>
       <c r="U8" s="0">
-        <v>9.0609897633627874</v>
+        <v>9.0488713145777968</v>
       </c>
       <c r="V8" s="0">
-        <v>8.8711011654241627</v>
+        <v>8.8385082484872797</v>
       </c>
       <c r="W8" s="0">
-        <v>8.7200588116519953</v>
+        <v>8.6717681013404953</v>
       </c>
       <c r="X8" s="0">
-        <v>8.5862573696166553</v>
+        <v>8.538443678377579</v>
       </c>
       <c r="Y8" s="0">
-        <v>8.4757101814587159</v>
+        <v>8.4285601280174039</v>
       </c>
       <c r="Z8" s="0">
-        <v>8.3822581027982288</v>
+        <v>8.3358379056426664</v>
       </c>
       <c r="AA8" s="0">
-        <v>8.3018184438006823</v>
+        <v>8.2565386182773839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>9.451280214325287</v>
+        <v>12.509011056149573</v>
       </c>
       <c r="B9" s="0">
-        <v>10.319411492864839</v>
+        <v>11.482052228974633</v>
       </c>
       <c r="C9" s="0">
-        <v>10.752674009029411</v>
+        <v>10.542165939779661</v>
       </c>
       <c r="D9" s="0">
-        <v>9.7802141663484825</v>
+        <v>9.9468320606150264</v>
       </c>
       <c r="E9" s="0">
-        <v>9.540502667192488</v>
+        <v>9.6612286475170031</v>
       </c>
       <c r="F9" s="0">
-        <v>9.2669915682210515</v>
+        <v>9.3433398302568396</v>
       </c>
       <c r="G9" s="0">
-        <v>9.0527962652444494</v>
+        <v>9.1084722446249629</v>
       </c>
       <c r="H9" s="0">
-        <v>9.4372404495201589</v>
+        <v>9.6501119343113828</v>
       </c>
       <c r="I9" s="0">
-        <v>10.494338689836615</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J9" s="0">
-        <v>11.251091074130811</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K9" s="0">
-        <v>11.102139979890151</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L9" s="0">
-        <v>11.078342038253641</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M9" s="0">
-        <v>11.061870217529753</v>
+        <v>10.989360509045326</v>
       </c>
       <c r="N9" s="0">
-        <v>11.024465370818911</v>
+        <v>10.936957079702742</v>
       </c>
       <c r="O9" s="0">
-        <v>10.911864133786374</v>
+        <v>10.811206520128733</v>
       </c>
       <c r="P9" s="0">
-        <v>10.730959140846709</v>
+        <v>10.620239677786842</v>
       </c>
       <c r="Q9" s="0">
-        <v>10.504166305813714</v>
+        <v>10.386141411507694</v>
       </c>
       <c r="R9" s="0">
-        <v>10.251506726523033</v>
+        <v>10.138897727695138</v>
       </c>
       <c r="S9" s="0">
-        <v>9.9893268743964239</v>
+        <v>9.8909692246157714</v>
       </c>
       <c r="T9" s="0">
-        <v>9.7297114693641635</v>
+        <v>9.6456566917560327</v>
       </c>
       <c r="U9" s="0">
-        <v>9.480725244697874</v>
+        <v>9.4100614938135436</v>
       </c>
       <c r="V9" s="0">
-        <v>9.255575923833069</v>
+        <v>9.196595221204694</v>
       </c>
       <c r="W9" s="0">
-        <v>9.0788438776652729</v>
+        <v>9.0273584653434344</v>
       </c>
       <c r="X9" s="0">
-        <v>8.9403292081386585</v>
+        <v>8.892060843977422</v>
       </c>
       <c r="Y9" s="0">
-        <v>8.8280704204679861</v>
+        <v>8.7804662680549246</v>
       </c>
       <c r="Z9" s="0">
-        <v>8.7347884426385267</v>
+        <v>8.6861468284544969</v>
       </c>
       <c r="AA9" s="0">
-        <v>8.655683380593425</v>
+        <v>8.6048556111754184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>10.05994590398921</v>
+        <v>10.844516223301909</v>
       </c>
       <c r="B10" s="0">
-        <v>10.96353224464325</v>
+        <v>9.9379482936889438</v>
       </c>
       <c r="C10" s="0">
-        <v>11.440108233108223</v>
+        <v>9.1112377092064634</v>
       </c>
       <c r="D10" s="0">
-        <v>9.1163278522964397</v>
+        <v>8.5954438328424629</v>
       </c>
       <c r="E10" s="0">
-        <v>8.8826739706186579</v>
+        <v>8.359478635847557</v>
       </c>
       <c r="F10" s="0">
-        <v>8.6198166718301348</v>
+        <v>8.0975678771514836</v>
       </c>
       <c r="G10" s="0">
-        <v>8.4205221338624021</v>
+        <v>7.9067622702830578</v>
       </c>
       <c r="H10" s="0">
-        <v>8.8709273527150625</v>
+        <v>8.4280112485773184</v>
       </c>
       <c r="I10" s="0">
-        <v>9.8068576809349732</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J10" s="0">
-        <v>10.45244529472383</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K10" s="0">
-        <v>10.297435374431931</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L10" s="0">
-        <v>10.275968773389657</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M10" s="0">
-        <v>10.259914782494828</v>
+        <v>9.6857505169184925</v>
       </c>
       <c r="N10" s="0">
-        <v>10.221751647215624</v>
+        <v>9.6415306014665223</v>
       </c>
       <c r="O10" s="0">
-        <v>10.089649734610973</v>
+        <v>9.5134814654599946</v>
       </c>
       <c r="P10" s="0">
-        <v>9.8521967167887681</v>
+        <v>9.2923310160848693</v>
       </c>
       <c r="Q10" s="0">
-        <v>9.5215843550905639</v>
+        <v>8.9991633327340139</v>
       </c>
       <c r="R10" s="0">
-        <v>9.1292209763954517</v>
+        <v>8.6615925544601407</v>
       </c>
       <c r="S10" s="0">
-        <v>8.7053504310970578</v>
+        <v>8.305524121181147</v>
       </c>
       <c r="T10" s="0">
-        <v>8.2754283308360375</v>
+        <v>7.9515979966360195</v>
       </c>
       <c r="U10" s="0">
-        <v>7.8600807296017452</v>
+        <v>7.614223762956029</v>
       </c>
       <c r="V10" s="0">
-        <v>7.4809968892007861</v>
+        <v>7.3106637621432533</v>
       </c>
       <c r="W10" s="0">
-        <v>7.1736496321381207</v>
+        <v>7.0715241739280925</v>
       </c>
       <c r="X10" s="0">
-        <v>6.9355972611229584</v>
+        <v>6.8918395718348222</v>
       </c>
       <c r="Y10" s="0">
-        <v>6.7528091032796036</v>
+        <v>6.7572780230578751</v>
       </c>
       <c r="Z10" s="0">
-        <v>6.6120988932004447</v>
+        <v>6.6551618579845275</v>
       </c>
       <c r="AA10" s="0">
-        <v>6.5025222878784632</v>
+        <v>6.5759159224898491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>9.7456956799205656</v>
+        <v>11.877427748784047</v>
       </c>
       <c r="B11" s="0">
-        <v>10.631212512896658</v>
+        <v>10.908563108108515</v>
       </c>
       <c r="C11" s="0">
-        <v>11.082721219304769</v>
+        <v>10.020654879047406</v>
       </c>
       <c r="D11" s="0">
-        <v>9.5324155660250352</v>
+        <v>9.4662077295226954</v>
       </c>
       <c r="E11" s="0">
-        <v>9.2675269815294428</v>
+        <v>9.2130073737036753</v>
       </c>
       <c r="F11" s="0">
-        <v>8.9922326865357594</v>
+        <v>8.9244193911582883</v>
       </c>
       <c r="G11" s="0">
-        <v>8.7732251075719177</v>
+        <v>8.7026070100774877</v>
       </c>
       <c r="H11" s="0">
-        <v>9.1850570691558637</v>
+        <v>9.2460677010700643</v>
       </c>
       <c r="I11" s="0">
-        <v>10.107495915644407</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J11" s="0">
-        <v>10.759004813883564</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K11" s="0">
-        <v>10.554294693454978</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L11" s="0">
-        <v>10.49182737581431</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M11" s="0">
-        <v>10.450000687802248</v>
+        <v>10.556062128182061</v>
       </c>
       <c r="N11" s="0">
-        <v>10.397112515272475</v>
+        <v>10.50999181108633</v>
       </c>
       <c r="O11" s="0">
-        <v>10.250113480476244</v>
+        <v>10.366331563923506</v>
       </c>
       <c r="P11" s="0">
-        <v>9.9995326777720202</v>
+        <v>10.113596692972683</v>
       </c>
       <c r="Q11" s="0">
-        <v>9.6587989985143885</v>
+        <v>9.7763065460635126</v>
       </c>
       <c r="R11" s="0">
-        <v>9.2755430131495444</v>
+        <v>9.3864887534988579</v>
       </c>
       <c r="S11" s="0">
-        <v>8.8589308724149643</v>
+        <v>8.9743263588901563</v>
       </c>
       <c r="T11" s="0">
-        <v>8.4469152549506941</v>
+        <v>8.5640798553505473</v>
       </c>
       <c r="U11" s="0">
-        <v>8.0425109682290561</v>
+        <v>8.1728562727950216</v>
       </c>
       <c r="V11" s="0">
-        <v>7.7064131342607451</v>
+        <v>7.8209233366775628</v>
       </c>
       <c r="W11" s="0">
-        <v>7.3949510114336947</v>
+        <v>7.5408471085344342</v>
       </c>
       <c r="X11" s="0">
-        <v>7.1586299769927777</v>
+        <v>7.3182913630253292</v>
       </c>
       <c r="Y11" s="0">
-        <v>6.9802453845707353</v>
+        <v>7.1727014797543438</v>
       </c>
       <c r="Z11" s="0">
-        <v>6.8598330447715465</v>
+        <v>7.0618200627300629</v>
       </c>
       <c r="AA11" s="0">
-        <v>6.7699663550647973</v>
+        <v>6.974041736290804</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>9.7071568814991629</v>
+        <v>12.509011056149573</v>
       </c>
       <c r="B12" s="0">
-        <v>10.582918549472272</v>
+        <v>11.482052228974633</v>
       </c>
       <c r="C12" s="0">
-        <v>11.022274147965094</v>
+        <v>10.542165939779661</v>
       </c>
       <c r="D12" s="0">
-        <v>9.7802141663484825</v>
+        <v>9.9468320606150264</v>
       </c>
       <c r="E12" s="0">
-        <v>9.540502667192488</v>
+        <v>9.6612286475170031</v>
       </c>
       <c r="F12" s="0">
-        <v>9.2669915682210515</v>
+        <v>9.3433398302568396</v>
       </c>
       <c r="G12" s="0">
-        <v>9.0527962652444494</v>
+        <v>9.1084722446249629</v>
       </c>
       <c r="H12" s="0">
-        <v>9.4372404495201589</v>
+        <v>9.6501119343113828</v>
       </c>
       <c r="I12" s="0">
-        <v>10.494338689836615</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J12" s="0">
-        <v>11.251091074130811</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K12" s="0">
-        <v>11.102139979890151</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L12" s="0">
-        <v>11.078342038253641</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M12" s="0">
-        <v>11.061870217529293</v>
+        <v>10.989360508636457</v>
       </c>
       <c r="N12" s="0">
-        <v>11.020330165862845</v>
+        <v>10.933972037672028</v>
       </c>
       <c r="O12" s="0">
-        <v>10.868640960984592</v>
+        <v>10.777380776585623</v>
       </c>
       <c r="P12" s="0">
-        <v>10.593292541351953</v>
+        <v>10.505057295035394</v>
       </c>
       <c r="Q12" s="0">
-        <v>10.224029150159879</v>
+        <v>10.140087980251458</v>
       </c>
       <c r="R12" s="0">
-        <v>9.7972768350457393</v>
+        <v>9.7272444195583194</v>
       </c>
       <c r="S12" s="0">
-        <v>9.3465636341822567</v>
+        <v>9.2963181603076066</v>
       </c>
       <c r="T12" s="0">
-        <v>8.8985733835961991</v>
+        <v>8.8672869793953328</v>
       </c>
       <c r="U12" s="0">
-        <v>8.4720206251843244</v>
+        <v>8.4580272650554136</v>
       </c>
       <c r="V12" s="0">
-        <v>8.0887051711935136</v>
+        <v>8.089646002584221</v>
       </c>
       <c r="W12" s="0">
-        <v>7.7892085311517381</v>
+        <v>7.7994469642251767</v>
       </c>
       <c r="X12" s="0">
-        <v>7.5671280446787703</v>
+        <v>7.5817793255801531</v>
       </c>
       <c r="Y12" s="0">
-        <v>7.4024233388518876</v>
+        <v>7.4189785409704445</v>
       </c>
       <c r="Z12" s="0">
-        <v>7.2786530438719019</v>
+        <v>7.2978856451317844</v>
       </c>
       <c r="AA12" s="0">
-        <v>7.1837730514246712</v>
+        <v>7.2057916015871069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>9.6857481685702975</v>
+        <v>10.844516223301909</v>
       </c>
       <c r="B13" s="0">
-        <v>10.556063619266631</v>
+        <v>9.9379482936889438</v>
       </c>
       <c r="C13" s="0">
-        <v>10.989359184768309</v>
+        <v>9.1112377092064634</v>
       </c>
       <c r="D13" s="0">
-        <v>9.1163278522964397</v>
+        <v>8.5954438328424629</v>
       </c>
       <c r="E13" s="0">
-        <v>8.8826739706186579</v>
+        <v>8.359478635847557</v>
       </c>
       <c r="F13" s="0">
-        <v>8.6198166718301348</v>
+        <v>8.0975678771514836</v>
       </c>
       <c r="G13" s="0">
-        <v>8.4205221338624021</v>
+        <v>7.9067622702830578</v>
       </c>
       <c r="H13" s="0">
-        <v>8.8709273527150625</v>
+        <v>8.4280112485773184</v>
       </c>
       <c r="I13" s="0">
-        <v>9.8068576809349732</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J13" s="0">
-        <v>10.45244529472383</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K13" s="0">
-        <v>10.297435374431931</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L13" s="0">
-        <v>10.275968773389657</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M13" s="0">
-        <v>10.259914782495276</v>
+        <v>9.6857505169180414</v>
       </c>
       <c r="N13" s="0">
-        <v>10.221616052250365</v>
+        <v>9.641498938986393</v>
       </c>
       <c r="O13" s="0">
-        <v>10.087373438855229</v>
+        <v>9.5122674552814193</v>
       </c>
       <c r="P13" s="0">
-        <v>9.8428377886044789</v>
+        <v>9.2862317965908279</v>
       </c>
       <c r="Q13" s="0">
-        <v>9.5057388146534869</v>
+        <v>8.9836018499515333</v>
       </c>
       <c r="R13" s="0">
-        <v>9.0967217296692482</v>
+        <v>8.6328261418529912</v>
       </c>
       <c r="S13" s="0">
-        <v>8.6497919827265797</v>
+        <v>8.2613272326940788</v>
       </c>
       <c r="T13" s="0">
-        <v>8.1956759460054691</v>
+        <v>7.8913256338135707</v>
       </c>
       <c r="U13" s="0">
-        <v>7.756064105260136</v>
+        <v>7.5385633168562558</v>
       </c>
       <c r="V13" s="0">
-        <v>7.354475645646323</v>
+        <v>7.2212917997889123</v>
       </c>
       <c r="W13" s="0">
-        <v>7.027250024731849</v>
+        <v>6.9711590385194278</v>
       </c>
       <c r="X13" s="0">
-        <v>6.7745301316129893</v>
+        <v>6.7841223471613787</v>
       </c>
       <c r="Y13" s="0">
-        <v>6.5827000600035452</v>
+        <v>6.6456799236031534</v>
       </c>
       <c r="Z13" s="0">
-        <v>6.4375345057630264</v>
+        <v>6.5423466806283237</v>
       </c>
       <c r="AA13" s="0">
-        <v>6.3270177878913145</v>
+        <v>6.4636788029153642</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>9.6583367335683992</v>
+        <v>11.877427748784047</v>
       </c>
       <c r="B14" s="0">
-        <v>10.529487424782483</v>
+        <v>10.908563108108515</v>
       </c>
       <c r="C14" s="0">
-        <v>10.954519144293071</v>
+        <v>10.020654879047406</v>
       </c>
       <c r="D14" s="0">
-        <v>9.5324155660250352</v>
+        <v>9.4662077295226954</v>
       </c>
       <c r="E14" s="0">
-        <v>9.2675269815294428</v>
+        <v>9.2130073737036753</v>
       </c>
       <c r="F14" s="0">
-        <v>8.9922326865357594</v>
+        <v>8.9244193911582883</v>
       </c>
       <c r="G14" s="0">
-        <v>8.7732251075719177</v>
+        <v>8.7026070100774877</v>
       </c>
       <c r="H14" s="0">
-        <v>9.1850570691558637</v>
+        <v>9.2460677010700643</v>
       </c>
       <c r="I14" s="0">
-        <v>10.107495915644407</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J14" s="0">
-        <v>10.759004813883564</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K14" s="0">
-        <v>10.554294693454978</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L14" s="0">
-        <v>10.49182737581431</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M14" s="0">
-        <v>10.450000687820225</v>
+        <v>10.556062128200541</v>
       </c>
       <c r="N14" s="0">
-        <v>10.397121314176928</v>
+        <v>10.510027955666276</v>
       </c>
       <c r="O14" s="0">
-        <v>10.249609000935893</v>
+        <v>10.365779971552536</v>
       </c>
       <c r="P14" s="0">
-        <v>9.9937385385763005</v>
+        <v>10.109373949585425</v>
       </c>
       <c r="Q14" s="0">
-        <v>9.6405372347932605</v>
+        <v>9.7641125575536361</v>
       </c>
       <c r="R14" s="0">
-        <v>9.2359464158095062</v>
+        <v>9.3625474414821355</v>
       </c>
       <c r="S14" s="0">
-        <v>8.8094867996454465</v>
+        <v>8.9361864064031007</v>
       </c>
       <c r="T14" s="0">
-        <v>8.3780684532936523</v>
+        <v>8.5107933407582674</v>
       </c>
       <c r="U14" s="0">
-        <v>7.9453014485494764</v>
+        <v>8.1048120951231493</v>
       </c>
       <c r="V14" s="0">
-        <v>7.5865935275363947</v>
+        <v>7.7241348314935818</v>
       </c>
       <c r="W14" s="0">
-        <v>7.2585357197532572</v>
+        <v>7.4196876233372748</v>
       </c>
       <c r="X14" s="0">
-        <v>7.010405908797094</v>
+        <v>7.2070946666351858</v>
       </c>
       <c r="Y14" s="0">
-        <v>6.8470993195191721</v>
+        <v>7.0494114058809014</v>
       </c>
       <c r="Z14" s="0">
-        <v>6.7288331964617205</v>
+        <v>6.9328740135197817</v>
       </c>
       <c r="AA14" s="0">
-        <v>6.6395319075559112</v>
+        <v>6.8472184355835743</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>9.629816237892733</v>
+        <v>12.509011056149573</v>
       </c>
       <c r="B15" s="0">
-        <v>10.502060557955398</v>
+        <v>11.482052228974633</v>
       </c>
       <c r="C15" s="0">
-        <v>10.920292510339333</v>
+        <v>10.542165939779661</v>
       </c>
       <c r="D15" s="0">
-        <v>9.7802141663484825</v>
+        <v>9.9468320606150264</v>
       </c>
       <c r="E15" s="0">
-        <v>9.540502667192488</v>
+        <v>9.6612286475170031</v>
       </c>
       <c r="F15" s="0">
-        <v>9.2669915682210515</v>
+        <v>9.3433398302568396</v>
       </c>
       <c r="G15" s="0">
-        <v>9.0527962652444494</v>
+        <v>9.1084722446249629</v>
       </c>
       <c r="H15" s="0">
-        <v>9.4372404495201589</v>
+        <v>9.6501119343113828</v>
       </c>
       <c r="I15" s="0">
-        <v>10.494338689836615</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J15" s="0">
-        <v>11.251091074130811</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K15" s="0">
-        <v>11.102139979890151</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L15" s="0">
-        <v>11.078342038253641</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M15" s="0">
-        <v>11.06187021754765</v>
+        <v>10.989360508691536</v>
       </c>
       <c r="N15" s="0">
-        <v>11.020299939936443</v>
+        <v>10.934078575323493</v>
       </c>
       <c r="O15" s="0">
-        <v>10.867357377950961</v>
+        <v>10.777189507284559</v>
       </c>
       <c r="P15" s="0">
-        <v>10.58668234793481</v>
+        <v>10.500826157372964</v>
       </c>
       <c r="Q15" s="0">
-        <v>10.206885594999093</v>
+        <v>10.12599203788402</v>
       </c>
       <c r="R15" s="0">
-        <v>9.7651785672737041</v>
+        <v>9.6966357374083145</v>
       </c>
       <c r="S15" s="0">
-        <v>9.2967445432372493</v>
+        <v>9.2479390673926574</v>
       </c>
       <c r="T15" s="0">
-        <v>8.830092175580079</v>
+        <v>8.800005466766228</v>
       </c>
       <c r="U15" s="0">
-        <v>8.3855444742873679</v>
+        <v>8.3723589307994821</v>
       </c>
       <c r="V15" s="0">
-        <v>7.9861405011231863</v>
+        <v>7.9873696982376758</v>
       </c>
       <c r="W15" s="0">
-        <v>7.6736929538939345</v>
+        <v>7.6839428253886748</v>
       </c>
       <c r="X15" s="0">
-        <v>7.4428330608564828</v>
+        <v>7.4570267318694317</v>
       </c>
       <c r="Y15" s="0">
-        <v>7.2733921307027369</v>
+        <v>7.2940140093404224</v>
       </c>
       <c r="Z15" s="0">
-        <v>7.1480742522364817</v>
+        <v>7.1736370496546762</v>
       </c>
       <c r="AA15" s="0">
-        <v>7.0538640276900484</v>
+        <v>7.0820283667117261</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>9.6020561261882307</v>
+        <v>10.844516223301909</v>
       </c>
       <c r="B16" s="0">
-        <v>10.475413709215777</v>
+        <v>9.9379482936889438</v>
       </c>
       <c r="C16" s="0">
-        <v>10.887683381502367</v>
+        <v>9.1112377092064634</v>
       </c>
       <c r="D16" s="0">
-        <v>9.1163278522964397</v>
+        <v>8.5954438328424629</v>
       </c>
       <c r="E16" s="0">
-        <v>8.8826739706186579</v>
+        <v>8.359478635847557</v>
       </c>
       <c r="F16" s="0">
-        <v>8.6198166718301348</v>
+        <v>8.0975678771514836</v>
       </c>
       <c r="G16" s="0">
-        <v>8.4205221338624021</v>
+        <v>7.9067622702830578</v>
       </c>
       <c r="H16" s="0">
-        <v>8.8709273527150625</v>
+        <v>8.4280112485773184</v>
       </c>
       <c r="I16" s="0">
-        <v>9.8068576809349732</v>
+        <v>9.4512827930285326</v>
       </c>
       <c r="J16" s="0">
-        <v>10.45244529472383</v>
+        <v>10.059940209892577</v>
       </c>
       <c r="K16" s="0">
-        <v>10.297435374431931</v>
+        <v>9.7456921436181183</v>
       </c>
       <c r="L16" s="0">
-        <v>10.275968773389657</v>
+        <v>9.7071548392781324</v>
       </c>
       <c r="M16" s="0">
-        <v>10.259914756059935</v>
+        <v>9.6857504789580737</v>
       </c>
       <c r="N16" s="0">
-        <v>10.204377763605772</v>
+        <v>9.6203702520837791</v>
       </c>
       <c r="O16" s="0">
-        <v>10.013836746195178</v>
+        <v>9.4248372274108725</v>
       </c>
       <c r="P16" s="0">
-        <v>9.6844219358344947</v>
+        <v>9.1080063052976481</v>
       </c>
       <c r="Q16" s="0">
-        <v>9.2356851052834248</v>
+        <v>8.6954879627832256</v>
       </c>
       <c r="R16" s="0">
-        <v>8.7079423468715831</v>
+        <v>8.2237083268006312</v>
       </c>
       <c r="S16" s="0">
-        <v>8.1467341732984053</v>
+        <v>7.7274534732952738</v>
       </c>
       <c r="T16" s="0">
-        <v>7.5742103606048437</v>
+        <v>7.2347518680153016</v>
       </c>
       <c r="U16" s="0">
-        <v>7.0156836473597117</v>
+        <v>6.7653580834004181</v>
       </c>
       <c r="V16" s="0">
-        <v>6.5245657628316751</v>
+        <v>6.3564656016758017</v>
       </c>
       <c r="W16" s="0">
-        <v>6.1484660830386844</v>
+        <v>6.0500063627802936</v>
       </c>
       <c r="X16" s="0">
-        <v>5.8675558750225454</v>
+        <v>5.8196755270846197</v>
       </c>
       <c r="Y16" s="0">
-        <v>5.64263543804684</v>
+        <v>5.648475850155811</v>
       </c>
       <c r="Z16" s="0">
-        <v>5.4718304355725769</v>
+        <v>5.5198771176215251</v>
       </c>
       <c r="AA16" s="0">
-        <v>5.3406445955222566</v>
+        <v>5.4211409809295734</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>9.5757842870622927</v>
+        <v>11.877427748784047</v>
       </c>
       <c r="B17" s="0">
-        <v>10.450229126585638</v>
+        <v>10.908563108108515</v>
       </c>
       <c r="C17" s="0">
-        <v>10.85705256498559</v>
+        <v>10.020654879047406</v>
       </c>
       <c r="D17" s="0">
-        <v>9.5324155660250352</v>
+        <v>9.4662077295226954</v>
       </c>
       <c r="E17" s="0">
-        <v>9.2675269815294428</v>
+        <v>9.2130073737036753</v>
       </c>
       <c r="F17" s="0">
-        <v>8.9922326865357594</v>
+        <v>8.9244193911582883</v>
       </c>
       <c r="G17" s="0">
-        <v>8.7732251075719177</v>
+        <v>8.7026070100774877</v>
       </c>
       <c r="H17" s="0">
-        <v>9.1850570691558637</v>
+        <v>9.2460677010700643</v>
       </c>
       <c r="I17" s="0">
-        <v>10.107495915644407</v>
+        <v>10.319418708629152</v>
       </c>
       <c r="J17" s="0">
-        <v>10.759004813883564</v>
+        <v>10.963453665753898</v>
       </c>
       <c r="K17" s="0">
-        <v>10.554294693454978</v>
+        <v>10.631276651974616</v>
       </c>
       <c r="L17" s="0">
-        <v>10.49182737581431</v>
+        <v>10.582915593864261</v>
       </c>
       <c r="M17" s="0">
-        <v>10.450000677969012</v>
+        <v>10.556062119052706</v>
       </c>
       <c r="N17" s="0">
-        <v>10.378513766282387</v>
+        <v>10.487013937810776</v>
       </c>
       <c r="O17" s="0">
-        <v>10.178064602308757</v>
+        <v>10.2704042137168</v>
       </c>
       <c r="P17" s="0">
-        <v>9.8412551482316619</v>
+        <v>9.9126944028536226</v>
       </c>
       <c r="Q17" s="0">
-        <v>9.3875552591690745</v>
+        <v>9.4437958789186904</v>
       </c>
       <c r="R17" s="0">
-        <v>8.882522185872892</v>
+        <v>8.9056738953275634</v>
       </c>
       <c r="S17" s="0">
-        <v>8.2953051611977155</v>
+        <v>8.3384079001131468</v>
       </c>
       <c r="T17" s="0">
-        <v>7.7311086099554247</v>
+        <v>7.7744623459915747</v>
       </c>
       <c r="U17" s="0">
-        <v>7.204711197547093</v>
+        <v>7.2369042995921982</v>
       </c>
       <c r="V17" s="0">
-        <v>6.7176631571453873</v>
+        <v>6.7676508673995084</v>
       </c>
       <c r="W17" s="0">
-        <v>6.3289318565400352</v>
+        <v>6.4139236031307139</v>
       </c>
       <c r="X17" s="0">
-        <v>6.0599082510577</v>
+        <v>6.1462372018877609</v>
       </c>
       <c r="Y17" s="0">
-        <v>5.8567667993533243</v>
+        <v>5.9455563217938296</v>
       </c>
       <c r="Z17" s="0">
-        <v>5.7019632802017108</v>
+        <v>5.7982807216121914</v>
       </c>
       <c r="AA17" s="0">
-        <v>5.5842240274323878</v>
+        <v>5.6850562941327629</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>9.5512601526152778</v>
+        <v>12.509011056149573</v>
       </c>
       <c r="B18" s="0">
-        <v>10.426785878807994</v>
+        <v>11.482052228974633</v>
       </c>
       <c r="C18" s="0">
-        <v>10.828492505416182</v>
+        <v>10.542165939779661</v>
       </c>
       <c r="D18" s="0">
-        <v>9.7802141663484825</v>
+        <v>9.9468320606150264</v>
       </c>
       <c r="E18" s="0">
-        <v>9.540502667192488</v>
+        <v>9.6612286475170031</v>
       </c>
       <c r="F18" s="0">
-        <v>9.2669915682210515</v>
+        <v>9.3433398302568396</v>
       </c>
       <c r="G18" s="0">
-        <v>9.0527962652444494</v>
+        <v>9.1084722446249629</v>
       </c>
       <c r="H18" s="0">
-        <v>9.4372404495201589</v>
+        <v>9.6501119343113828</v>
       </c>
       <c r="I18" s="0">
-        <v>10.494338689836615</v>
+        <v>10.752678081056965</v>
       </c>
       <c r="J18" s="0">
-        <v>11.251091074130811</v>
+        <v>11.440037879892893</v>
       </c>
       <c r="K18" s="0">
-        <v>11.102139979890151</v>
+        <v>11.082788495871069</v>
       </c>
       <c r="L18" s="0">
-        <v>11.078342038253641</v>
+        <v>11.022276467660486</v>
       </c>
       <c r="M18" s="0">
-        <v>11.061870161490837</v>
+        <v>10.989360535412917</v>
       </c>
       <c r="N18" s="0">
-        <v>11.001513189122269</v>
+        <v>10.910065964080198</v>
       </c>
       <c r="O18" s="0">
-        <v>10.785357800401759</v>
+        <v>10.677682038651943</v>
       </c>
       <c r="P18" s="0">
-        <v>10.407186571369959</v>
+        <v>10.294644783408645</v>
       </c>
       <c r="Q18" s="0">
-        <v>9.9047453139813051</v>
+        <v>9.7936337546111378</v>
       </c>
       <c r="R18" s="0">
-        <v>9.3262187368146598</v>
+        <v>9.2381838893246755</v>
       </c>
       <c r="S18" s="0">
-        <v>8.7163289986867589</v>
+        <v>8.6498369246432478</v>
       </c>
       <c r="T18" s="0">
-        <v>8.1109749233183273</v>
+        <v>8.0624529886563288</v>
       </c>
       <c r="U18" s="0">
-        <v>7.5355220742237101</v>
+        <v>7.5007894220962532</v>
       </c>
       <c r="V18" s="0">
-        <v>7.0300127458991932</v>
+        <v>7.0083436980780975</v>
       </c>
       <c r="W18" s="0">
-        <v>6.6441618755282006</v>
+        <v>6.648027902160444</v>
       </c>
       <c r="X18" s="0">
-        <v>6.3587251852319593</v>
+        <v>6.383454654467382</v>
       </c>
       <c r="Y18" s="0">
-        <v>6.1484042388287481</v>
+        <v>6.1945070784080176</v>
       </c>
       <c r="Z18" s="0">
-        <v>5.9916445117931696</v>
+        <v>6.0521562999291181</v>
       </c>
       <c r="AA18" s="0">
-        <v>5.8725513471193365</v>
+        <v>5.9423975863583811</v>
       </c>
     </row>
     <row r="19">
